--- a/Base_de_donnees/Fichiers_metadonnees/Remplissage_des_tables_liees_aux_capteurs.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Remplissage_des_tables_liees_aux_capteurs.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t xml:space="preserve">numéro_serie</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">description (unique)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">num_colonne</t>
   </si>
   <si>
     <t xml:space="preserve">2024/05/20</t>
@@ -189,8 +192,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="0"/>
     </font>
@@ -254,15 +257,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -453,11 +456,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.52"/>
@@ -603,20 +605,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="85.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.38"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -626,29 +627,37 @@
       <c r="C1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="E1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
+      <c r="B2" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -656,10 +665,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -676,11 +688,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.48"/>
@@ -691,19 +702,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -714,30 +725,30 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>21</v>
+      <c r="A3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -754,11 +765,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.62"/>
@@ -768,35 +778,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
+      <c r="B2" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>0.11</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -813,11 +823,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.88"/>
@@ -825,10 +834,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -838,14 +847,14 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>27</v>
+      <c r="A2" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
